--- a/backend/src/templates/Monetique-template.xlsx
+++ b/backend/src/templates/Monetique-template.xlsx
@@ -1,26 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\template\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082B499D-74DD-4FD5-A1A8-C2B253AD3C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Feuil3" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Feuil3" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
   <si>
     <t>Feuille de présence mission</t>
   </si>
@@ -164,6 +155,9 @@
   </si>
   <si>
     <t>Responsable suivi de mission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEJAOUI Feriel </t>
   </si>
   <si>
     <t xml:space="preserve">  </t>
@@ -178,80 +172,77 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="164" formatCode="D/M/YYYY"/>
   </numFmts>
   <fonts count="13">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF4F6228"/>
       <name val="Arial Black"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
+    <font/>
     <font>
       <b/>
-      <sz val="8"/>
+      <sz val="8.0"/>
       <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial Narrow"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="9.0"/>
       <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="16.0"/>
       <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial Narrow"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="8.0"/>
       <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
     </font>
@@ -261,7 +252,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -295,35 +286,22 @@
     </fill>
   </fills>
   <borders count="24">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="medium">
         <color rgb="FF76923C"/>
       </left>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="hair">
@@ -338,12 +316,19 @@
       <bottom style="hair">
         <color rgb="FFE4EDD3"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="hair">
         <color rgb="FFE4EDD3"/>
       </left>
+      <top style="hair">
+        <color rgb="FFE4EDD3"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FFE4EDD3"/>
+      </bottom>
+    </border>
+    <border>
       <right/>
       <top style="hair">
         <color rgb="FFE4EDD3"/>
@@ -351,18 +336,6 @@
       <bottom style="hair">
         <color rgb="FFE4EDD3"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color rgb="FFE4EDD3"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FFE4EDD3"/>
-      </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -377,23 +350,19 @@
       <bottom style="hair">
         <color rgb="FF9BBB59"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="hair">
         <color rgb="FF9BBB59"/>
       </left>
-      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="hair">
         <color rgb="FF9BBB59"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="hair">
         <color rgb="FF9BBB59"/>
       </right>
@@ -403,7 +372,6 @@
       <bottom style="hair">
         <color rgb="FF9BBB59"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="hair">
@@ -416,7 +384,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -431,23 +398,19 @@
       <bottom style="hair">
         <color rgb="FF9BBB59"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="hair">
         <color rgb="FF9BBB59"/>
       </left>
-      <right/>
       <top style="hair">
         <color rgb="FF9BBB59"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -457,7 +420,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -472,18 +434,14 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="hair">
         <color rgb="FF9BBB59"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -498,14 +456,12 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -518,7 +474,6 @@
       <bottom style="thin">
         <color rgb="FF9BBB59"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -533,7 +488,6 @@
       <bottom style="thin">
         <color rgb="FF9BBB59"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -546,7 +500,6 @@
       <bottom style="thin">
         <color rgb="FF9BBB59"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -558,8 +511,6 @@
       <top style="thin">
         <color rgb="FF9BBB59"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -568,11 +519,9 @@
       <right style="thin">
         <color rgb="FF9BBB59"/>
       </right>
-      <top/>
       <bottom style="thin">
         <color rgb="FF9BBB59"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -581,123 +530,120 @@
       <right style="thin">
         <color rgb="FF9BBB59"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="38">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="5" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="5" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="5" fillId="2" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="8" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="11" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="12" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="14" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="11" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="16" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="17" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf borderId="18" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="19" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="19" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="20" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="19" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="19" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="19" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="21" fillId="0" fontId="12" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="22" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="21" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="21" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf borderId="23" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -705,7 +651,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -895,433 +841,430 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="3" width="39.6640625" customWidth="1"/>
-    <col min="4" max="4" width="36.44140625" customWidth="1"/>
-    <col min="5" max="26" width="9.109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="33.43"/>
+    <col customWidth="1" min="2" max="3" width="39.71"/>
+    <col customWidth="1" min="4" max="4" width="36.43"/>
+    <col customWidth="1" min="5" max="26" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.25" customHeight="1">
+    <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="21" customHeight="1">
-      <c r="A2" s="19" t="s">
+    <row r="2" ht="21.0" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="21"/>
-    </row>
-    <row r="3" spans="1:4" ht="14.25" customHeight="1"/>
-    <row r="4" spans="1:4" ht="14.25" customHeight="1">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" ht="14.25" customHeight="1"/>
+    <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A5" s="2" t="s">
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="23"/>
-    </row>
-    <row r="6" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A6" s="3" t="s">
+      <c r="C5" s="7"/>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="23"/>
-    </row>
-    <row r="7" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="C6" s="7"/>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="23"/>
-    </row>
-    <row r="8" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A8" s="3" t="s">
+      <c r="C7" s="7"/>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="23"/>
-    </row>
-    <row r="9" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A9" s="2" t="s">
+      <c r="C8" s="7"/>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="23"/>
-    </row>
-    <row r="10" spans="1:4" ht="14.25" customHeight="1">
+      <c r="C9" s="7"/>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="14.25" customHeight="1">
+    <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A12" s="4" t="s">
+    <row r="12" ht="20.25" customHeight="1">
+      <c r="A12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="5" t="s">
+      <c r="C12" s="14"/>
+      <c r="D12" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1">
-      <c r="A13" s="6" t="s">
+    <row r="13" ht="18.0" customHeight="1">
+      <c r="A13" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="7"/>
-    </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1">
-      <c r="A14" s="6" t="s">
+      <c r="B13" s="17"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="19"/>
+    </row>
+    <row r="14" ht="18.0" customHeight="1">
+      <c r="A14" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="7"/>
-    </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1">
-      <c r="A15" s="6" t="s">
+      <c r="B14" s="17"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="19"/>
+    </row>
+    <row r="15" ht="18.0" customHeight="1">
+      <c r="A15" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="7"/>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A16" s="6" t="s">
+      <c r="B15" s="17"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="19"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="7"/>
-    </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1">
-      <c r="A17" s="6" t="s">
+      <c r="B16" s="17"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" ht="18.0" customHeight="1">
+      <c r="A17" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="29"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="7"/>
-    </row>
-    <row r="18" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A18" s="6" t="s">
+      <c r="B17" s="17"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" ht="20.25" customHeight="1">
+      <c r="A18" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="7"/>
-    </row>
-    <row r="19" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A19" s="6" t="s">
+      <c r="B18" s="17"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" ht="20.25" customHeight="1">
+      <c r="A19" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="7"/>
-    </row>
-    <row r="20" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A20" s="6" t="s">
+      <c r="B19" s="17"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" ht="20.25" customHeight="1">
+      <c r="A20" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="7"/>
-    </row>
-    <row r="21" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A21" s="6" t="s">
+      <c r="B20" s="17"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="19"/>
+    </row>
+    <row r="21" ht="20.25" customHeight="1">
+      <c r="A21" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="7"/>
-    </row>
-    <row r="22" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A22" s="6" t="s">
+      <c r="B21" s="17"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="19"/>
+    </row>
+    <row r="22" ht="20.25" customHeight="1">
+      <c r="A22" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="7"/>
-    </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1">
-      <c r="A23" s="6" t="s">
+      <c r="B22" s="17"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="19"/>
+    </row>
+    <row r="23" ht="18.0" customHeight="1">
+      <c r="A23" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="7"/>
-    </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1">
-      <c r="A24" s="6" t="s">
+      <c r="B23" s="17"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="19"/>
+    </row>
+    <row r="24" ht="18.0" customHeight="1">
+      <c r="A24" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="29"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="7"/>
-    </row>
-    <row r="25" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A25" s="6" t="s">
+      <c r="B24" s="17"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="19"/>
+    </row>
+    <row r="25" ht="20.25" customHeight="1">
+      <c r="A25" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="7"/>
-    </row>
-    <row r="26" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A26" s="6" t="s">
+      <c r="B25" s="17"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="19"/>
+    </row>
+    <row r="26" ht="20.25" customHeight="1">
+      <c r="A26" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="7"/>
-    </row>
-    <row r="27" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A27" s="6" t="s">
+      <c r="B26" s="17"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="19"/>
+    </row>
+    <row r="27" ht="20.25" customHeight="1">
+      <c r="A27" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="7"/>
-    </row>
-    <row r="28" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A28" s="6" t="s">
+      <c r="B27" s="17"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="19"/>
+    </row>
+    <row r="28" ht="20.25" customHeight="1">
+      <c r="A28" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="7"/>
-    </row>
-    <row r="29" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A29" s="6" t="s">
+      <c r="B28" s="17"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="19"/>
+    </row>
+    <row r="29" ht="20.25" customHeight="1">
+      <c r="A29" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="7"/>
-    </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1">
-      <c r="A30" s="6" t="s">
+      <c r="B29" s="17"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="19"/>
+    </row>
+    <row r="30" ht="18.0" customHeight="1">
+      <c r="A30" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="7"/>
-    </row>
-    <row r="31" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A31" s="6" t="s">
+      <c r="B30" s="17"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="19"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="29"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="7"/>
-    </row>
-    <row r="32" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A32" s="6" t="s">
+      <c r="B31" s="17"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="19"/>
+    </row>
+    <row r="32" ht="20.25" customHeight="1">
+      <c r="A32" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="7"/>
-    </row>
-    <row r="33" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A33" s="6" t="s">
+      <c r="B32" s="17"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="19"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="29"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="7"/>
-    </row>
-    <row r="34" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A34" s="6" t="s">
+      <c r="B33" s="17"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="19"/>
+    </row>
+    <row r="34" ht="20.25" customHeight="1">
+      <c r="A34" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="29"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="7"/>
-    </row>
-    <row r="35" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A35" s="6" t="s">
+      <c r="B34" s="17"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="19"/>
+    </row>
+    <row r="35" ht="20.25" customHeight="1">
+      <c r="A35" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="7"/>
-    </row>
-    <row r="36" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A36" s="6" t="s">
+      <c r="B35" s="17"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="19"/>
+    </row>
+    <row r="36" ht="20.25" customHeight="1">
+      <c r="A36" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="29"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="7"/>
-    </row>
-    <row r="37" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A37" s="8" t="s">
+      <c r="B36" s="17"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="19"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="7"/>
-    </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1">
-      <c r="A38" s="6" t="s">
+      <c r="B37" s="17"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="19"/>
+    </row>
+    <row r="38" ht="18.0" customHeight="1">
+      <c r="A38" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="29"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="7"/>
-    </row>
-    <row r="39" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A39" s="6" t="s">
+      <c r="B38" s="17"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="19"/>
+    </row>
+    <row r="39" ht="20.25" customHeight="1">
+      <c r="A39" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="29"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="7"/>
-    </row>
-    <row r="40" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A40" s="9" t="s">
+      <c r="B39" s="17"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="19"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="7"/>
-    </row>
-    <row r="41" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A41" s="9" t="s">
+      <c r="B40" s="17"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="19"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="29"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="7"/>
-    </row>
-    <row r="42" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A42" s="9" t="s">
+      <c r="B41" s="17"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="19"/>
+    </row>
+    <row r="42" ht="20.25" customHeight="1">
+      <c r="A42" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B42" s="29"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="7"/>
-    </row>
-    <row r="43" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A43" s="9" t="s">
+      <c r="B42" s="17"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="19"/>
+    </row>
+    <row r="43" ht="20.25" customHeight="1">
+      <c r="A43" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="7"/>
-    </row>
-    <row r="44" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A44" s="10"/>
-      <c r="B44" s="11" t="s">
+      <c r="B43" s="17"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="19"/>
+    </row>
+    <row r="44" ht="20.25" customHeight="1">
+      <c r="A44" s="24"/>
+      <c r="B44" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C44" s="12"/>
-      <c r="D44" s="13"/>
-    </row>
-    <row r="45" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A45" s="10"/>
-      <c r="B45" s="11" t="s">
+      <c r="C44" s="26"/>
+      <c r="D44" s="27"/>
+    </row>
+    <row r="45" ht="20.25" customHeight="1">
+      <c r="A45" s="24"/>
+      <c r="B45" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="12"/>
-      <c r="D45" s="13"/>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1">
-      <c r="B46" s="14" t="s">
+      <c r="C45" s="26"/>
+      <c r="D45" s="27"/>
+    </row>
+    <row r="46" ht="15.0" customHeight="1">
+      <c r="B46" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="29" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1">
-      <c r="B47" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="17" t="s">
+    <row r="47" ht="15.0" customHeight="1">
+      <c r="B47" s="30" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1">
-      <c r="B48" s="14" t="s">
+      <c r="C47" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" ht="15" customHeight="1">
-      <c r="B49" s="32"/>
-      <c r="C49" s="32"/>
-    </row>
-    <row r="50" spans="2:3" ht="14.25" customHeight="1">
-      <c r="B50" s="33"/>
-      <c r="C50" s="33"/>
-    </row>
-    <row r="51" spans="2:3" ht="14.25" customHeight="1">
-      <c r="B51" s="14" t="s">
+    </row>
+    <row r="48" ht="15.0" customHeight="1">
+      <c r="B48" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="C51" s="18" t="s">
+      <c r="C48" s="32" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="2:3" ht="14.25" customHeight="1">
-      <c r="B52" s="34"/>
+    <row r="49" ht="15.0" customHeight="1">
+      <c r="B49" s="33"/>
+      <c r="C49" s="33"/>
+    </row>
+    <row r="50" ht="14.25" customHeight="1">
+      <c r="B50" s="34"/>
+      <c r="C50" s="34"/>
+    </row>
+    <row r="51" ht="14.25" customHeight="1">
+      <c r="B51" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51" s="32" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" ht="14.25" customHeight="1">
+      <c r="B52" s="35"/>
       <c r="C52" s="36"/>
     </row>
-    <row r="53" spans="2:3" ht="14.25" customHeight="1">
-      <c r="B53" s="35"/>
-      <c r="C53" s="35"/>
-    </row>
-    <row r="54" spans="2:3" ht="14.25" customHeight="1">
-      <c r="B54" s="33"/>
-      <c r="C54" s="33"/>
-    </row>
-    <row r="55" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="56" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="57" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="58" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="59" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="60" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="61" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="62" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="63" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="64" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="53" ht="14.25" customHeight="1">
+      <c r="B53" s="37"/>
+      <c r="C53" s="37"/>
+    </row>
+    <row r="54" ht="14.25" customHeight="1">
+      <c r="B54" s="34"/>
+      <c r="C54" s="34"/>
+    </row>
+    <row r="55" ht="14.25" customHeight="1"/>
+    <row r="56" ht="14.25" customHeight="1"/>
+    <row r="57" ht="14.25" customHeight="1"/>
+    <row r="58" ht="14.25" customHeight="1"/>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1"/>
+    <row r="61" ht="14.25" customHeight="1"/>
+    <row r="62" ht="14.25" customHeight="1"/>
+    <row r="63" ht="14.25" customHeight="1"/>
+    <row r="64" ht="14.25" customHeight="1"/>
     <row r="65" ht="14.25" customHeight="1"/>
     <row r="66" ht="14.25" customHeight="1"/>
     <row r="67" ht="14.25" customHeight="1"/>
@@ -2260,16 +2203,41 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="C49:C50"/>
     <mergeCell ref="B52:B54"/>
     <mergeCell ref="C52:C54"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
@@ -2277,37 +2245,14 @@
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
   </mergeCells>
-  <pageMargins left="0.51181102362204722" right="0.31496062992125984" top="0.35433070866141736" bottom="0.35433070866141736" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.35433070866141736" footer="0.0" header="0.0" left="0.5118110236220472" right="0.31496062992125984" top="0.35433070866141736"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L06-049DIRECTION SYSTEME D'INFORMATION</oddHeader>
     <oddFooter>&amp;RPage &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/backend/src/templates/Monetique-template.xlsx
+++ b/backend/src/templates/Monetique-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\excellia-app\backend\src\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{333B49C9-1D04-4614-B336-04F96F16DDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388379EC-2C9A-4352-AB57-BBFAA11147AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -286,7 +286,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -498,13 +498,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF9BBB59"/>
       </left>
@@ -573,7 +566,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -599,25 +592,19 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -656,15 +643,15 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -692,9 +679,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2743200" cy="1318260"/>
     <xdr:pic>
@@ -716,7 +703,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2293620" y="14813280"/>
+          <a:off x="2339340" y="15316200"/>
           <a:ext cx="2743200" cy="1318260"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -935,7 +922,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D997"/>
+  <dimension ref="A1:D996"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.44140625" customWidth="1"/>
@@ -949,12 +936,12 @@
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="21" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
     </row>
     <row r="3" spans="1:4" ht="14.25" customHeight="1"/>
     <row r="4" spans="1:4" ht="14.25" customHeight="1">
@@ -965,46 +952,46 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="19"/>
+      <c r="C5" s="17"/>
     </row>
     <row r="6" spans="1:4" ht="14.25" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="19"/>
+      <c r="C6" s="17"/>
     </row>
     <row r="7" spans="1:4" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="19"/>
+      <c r="C7" s="17"/>
     </row>
     <row r="8" spans="1:4" ht="14.25" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="19"/>
+      <c r="C8" s="17"/>
     </row>
     <row r="9" spans="1:4" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="19"/>
+      <c r="C9" s="17"/>
     </row>
     <row r="10" spans="1:4" ht="14.25" customHeight="1">
       <c r="A10" s="1"/>
@@ -1018,10 +1005,10 @@
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="24"/>
+      <c r="C12" s="22"/>
       <c r="D12" s="5" t="s">
         <v>13</v>
       </c>
@@ -1030,10 +1017,10 @@
       <c r="A13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="26"/>
+      <c r="B13" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="24"/>
       <c r="D13" s="7" t="s">
         <v>15</v>
       </c>
@@ -1042,10 +1029,10 @@
       <c r="A14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="26"/>
+      <c r="B14" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="24"/>
       <c r="D14" s="7" t="s">
         <v>15</v>
       </c>
@@ -1054,10 +1041,10 @@
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="26"/>
+      <c r="B15" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="24"/>
       <c r="D15" s="8" t="s">
         <v>15</v>
       </c>
@@ -1066,10 +1053,10 @@
       <c r="A16" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="26"/>
+      <c r="B16" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="24"/>
       <c r="D16" s="8" t="s">
         <v>15</v>
       </c>
@@ -1078,10 +1065,10 @@
       <c r="A17" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="26"/>
+      <c r="B17" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="24"/>
       <c r="D17" s="8" t="s">
         <v>15</v>
       </c>
@@ -1090,10 +1077,10 @@
       <c r="A18" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="26"/>
+      <c r="B18" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="24"/>
       <c r="D18" s="8" t="s">
         <v>15</v>
       </c>
@@ -1102,10 +1089,10 @@
       <c r="A19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="26"/>
+      <c r="B19" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="24"/>
       <c r="D19" s="8" t="s">
         <v>15</v>
       </c>
@@ -1114,10 +1101,10 @@
       <c r="A20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="26"/>
+      <c r="B20" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="24"/>
       <c r="D20" s="8" t="s">
         <v>15</v>
       </c>
@@ -1126,10 +1113,10 @@
       <c r="A21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="26"/>
+      <c r="B21" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="24"/>
       <c r="D21" s="8" t="s">
         <v>15</v>
       </c>
@@ -1138,10 +1125,10 @@
       <c r="A22" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="26"/>
+      <c r="B22" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="24"/>
       <c r="D22" s="8" t="s">
         <v>15</v>
       </c>
@@ -1150,10 +1137,10 @@
       <c r="A23" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="26"/>
+      <c r="B23" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="24"/>
       <c r="D23" s="8" t="s">
         <v>15</v>
       </c>
@@ -1162,10 +1149,10 @@
       <c r="A24" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="26"/>
+      <c r="B24" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="24"/>
       <c r="D24" s="8" t="s">
         <v>15</v>
       </c>
@@ -1174,10 +1161,10 @@
       <c r="A25" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="26"/>
+      <c r="B25" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="24"/>
       <c r="D25" s="8" t="s">
         <v>15</v>
       </c>
@@ -1186,10 +1173,10 @@
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="26"/>
+      <c r="B26" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="24"/>
       <c r="D26" s="8" t="s">
         <v>15</v>
       </c>
@@ -1198,10 +1185,10 @@
       <c r="A27" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="29"/>
+      <c r="B27" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="27"/>
       <c r="D27" s="8" t="s">
         <v>15</v>
       </c>
@@ -1210,48 +1197,48 @@
       <c r="A28" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="30"/>
-      <c r="C28" s="31"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="29"/>
       <c r="D28" s="8"/>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1">
       <c r="A29" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="31"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="29"/>
       <c r="D29" s="8"/>
     </row>
     <row r="30" spans="1:4" ht="30" customHeight="1">
       <c r="A30" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="31"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="29"/>
       <c r="D30" s="8"/>
     </row>
     <row r="31" spans="1:4" ht="30" customHeight="1">
       <c r="A31" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="30"/>
-      <c r="C31" s="31"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="29"/>
       <c r="D31" s="8"/>
     </row>
     <row r="32" spans="1:4" ht="30" customHeight="1">
       <c r="A32" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="31"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="29"/>
       <c r="D32" s="8"/>
     </row>
     <row r="33" spans="1:4" ht="30" customHeight="1">
       <c r="A33" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="30"/>
-      <c r="C33" s="31"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="29"/>
       <c r="D33" s="8" t="s">
         <v>15</v>
       </c>
@@ -1260,10 +1247,10 @@
       <c r="A34" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" s="31"/>
+      <c r="B34" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="29"/>
       <c r="D34" s="8" t="s">
         <v>15</v>
       </c>
@@ -1272,10 +1259,10 @@
       <c r="A35" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C35" s="26"/>
+      <c r="B35" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="24"/>
       <c r="D35" s="8" t="s">
         <v>15</v>
       </c>
@@ -1284,10 +1271,10 @@
       <c r="A36" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36" s="26"/>
+      <c r="B36" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="24"/>
       <c r="D36" s="8" t="s">
         <v>15</v>
       </c>
@@ -1296,10 +1283,10 @@
       <c r="A37" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C37" s="26"/>
+      <c r="B37" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="24"/>
       <c r="D37" s="8" t="s">
         <v>15</v>
       </c>
@@ -1308,10 +1295,10 @@
       <c r="A38" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" s="26"/>
+      <c r="B38" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="24"/>
       <c r="D38" s="8" t="s">
         <v>15</v>
       </c>
@@ -1320,10 +1307,10 @@
       <c r="A39" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C39" s="26"/>
+      <c r="B39" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="24"/>
       <c r="D39" s="8" t="s">
         <v>15</v>
       </c>
@@ -1332,99 +1319,110 @@
       <c r="A40" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C40" s="26"/>
+      <c r="B40" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="24"/>
       <c r="D40" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="30" customHeight="1">
-      <c r="A41" s="9"/>
-      <c r="B41" s="10" t="s">
+      <c r="A41" s="6"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="8"/>
+    </row>
+    <row r="42" spans="1:4" ht="30" customHeight="1">
+      <c r="A42" s="6"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="8"/>
+    </row>
+    <row r="43" spans="1:4" ht="20.399999999999999">
+      <c r="A43" s="6"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="8"/>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1">
+      <c r="B44" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C44" s="10">
         <v>0</v>
       </c>
-      <c r="D41" s="12"/>
-    </row>
-    <row r="42" spans="1:4" ht="30" customHeight="1">
-      <c r="A42" s="9"/>
-      <c r="B42" s="10" t="s">
+    </row>
+    <row r="45" spans="1:4" ht="15" customHeight="1">
+      <c r="B45" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C45" s="10">
         <v>0</v>
       </c>
-      <c r="D42" s="12"/>
-    </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1">
-      <c r="B43" s="13" t="s">
+    </row>
+    <row r="46" spans="1:4" ht="14.25" customHeight="1">
+      <c r="B46" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C46" s="12" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1">
-      <c r="B44" s="15" t="s">
+    <row r="47" spans="1:4" ht="14.25" customHeight="1">
+      <c r="B47" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="15"/>
-    </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1">
-      <c r="B45" s="13" t="s">
+      <c r="C47" s="13"/>
+    </row>
+    <row r="48" spans="1:4" ht="14.25" customHeight="1">
+      <c r="B48" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C48" s="12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1">
-      <c r="B46" s="32"/>
-      <c r="C46" s="32"/>
-    </row>
-    <row r="47" spans="1:4" ht="14.25" customHeight="1">
-      <c r="B47" s="33"/>
-      <c r="C47" s="33"/>
-    </row>
-    <row r="48" spans="1:4" ht="14.25" customHeight="1">
-      <c r="B48" s="13" t="s">
+    <row r="49" spans="2:3" ht="14.25" customHeight="1">
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+    </row>
+    <row r="50" spans="2:3" ht="14.25" customHeight="1">
+      <c r="B50" s="31"/>
+      <c r="C50" s="31"/>
+    </row>
+    <row r="51" spans="2:3" ht="14.25" customHeight="1">
+      <c r="B51" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="14" t="s">
+      <c r="C51" s="12" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="2:3" ht="14.25" customHeight="1">
-      <c r="B49" s="36"/>
-      <c r="C49" s="34"/>
-    </row>
-    <row r="50" spans="2:3" ht="14.25" customHeight="1">
-      <c r="B50" s="35"/>
-      <c r="C50" s="35"/>
-    </row>
-    <row r="51" spans="2:3" ht="14.25" customHeight="1">
-      <c r="B51" s="35"/>
-      <c r="C51" s="35"/>
-    </row>
     <row r="52" spans="2:3" ht="14.25" customHeight="1">
-      <c r="B52" s="35"/>
-      <c r="C52" s="35"/>
+      <c r="B52" s="34"/>
+      <c r="C52" s="32"/>
     </row>
     <row r="53" spans="2:3" ht="14.25" customHeight="1">
-      <c r="B53" s="35"/>
-      <c r="C53" s="35"/>
+      <c r="B53" s="33"/>
+      <c r="C53" s="33"/>
     </row>
     <row r="54" spans="2:3" ht="14.25" customHeight="1">
       <c r="B54" s="33"/>
       <c r="C54" s="33"/>
     </row>
-    <row r="55" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="56" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="57" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="55" spans="2:3" ht="14.25" customHeight="1">
+      <c r="B55" s="33"/>
+      <c r="C55" s="33"/>
+    </row>
+    <row r="56" spans="2:3" ht="14.25" customHeight="1">
+      <c r="B56" s="33"/>
+      <c r="C56" s="33"/>
+    </row>
+    <row r="57" spans="2:3" ht="14.25" customHeight="1">
+      <c r="B57" s="31"/>
+      <c r="C57" s="31"/>
+    </row>
     <row r="58" spans="2:3" ht="14.25" customHeight="1"/>
     <row r="59" spans="2:3" ht="14.25" customHeight="1"/>
     <row r="60" spans="2:3" ht="14.25" customHeight="1"/>
@@ -1615,7 +1613,7 @@
     <row r="245" ht="14.25" customHeight="1"/>
     <row r="246" ht="14.25" customHeight="1"/>
     <row r="247" ht="14.25" customHeight="1"/>
-    <row r="248" ht="14.25" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
     <row r="249" ht="15.75" customHeight="1"/>
     <row r="250" ht="15.75" customHeight="1"/>
     <row r="251" ht="15.75" customHeight="1"/>
@@ -2364,11 +2362,10 @@
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
     <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="C49:C54"/>
-    <mergeCell ref="B49:B54"/>
+  <mergeCells count="42">
+    <mergeCell ref="C52:C57"/>
+    <mergeCell ref="B52:B57"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
@@ -2376,11 +2373,14 @@
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B28:C28"/>
